--- a/ORDER_MGMT/regular_order_mgmt/order_files/Mapped_Expired_latest_OrderBook_Equity_23july2026_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/Mapped_Expired_latest_OrderBook_Equity_23july2026_Thurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2758DBC-BAF6-4642-B7A7-C4473C4F9F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42909CF8-7A1E-446B-A743-5FFAED5A1B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -607,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -743,7 +743,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -760,7 +760,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -794,7 +794,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -828,7 +828,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -845,7 +845,7 @@
         <v>1023.9</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -862,7 +862,7 @@
         <v>1011.9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -879,7 +879,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -896,7 +896,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>25</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -2498,9 +2498,7 @@
   <autoFilter ref="B1:B112" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="VBLEQ"/>
-        <filter val="WAAREERTLEQ"/>
-        <filter val="ZENTECEQ"/>
+        <filter val="NAM-INDIAEQ"/>
       </filters>
     </filterColumn>
   </autoFilter>
